--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -13645,7 +13645,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23803,7 +23803,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24353,7 +24353,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -24903,7 +24903,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -25453,7 +25453,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26003,7 +26003,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -26553,7 +26553,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -29039,7 +29039,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -29589,7 +29589,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -30139,7 +30139,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -30689,7 +30689,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -31239,7 +31239,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -32875,16 +32875,16 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O179" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q179" t="n">
         <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>0.208593237428971</v>
+        <v>0.2129389298754079</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -33037,10 +33037,10 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O180" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U180" t="inlineStr">
         <is>
@@ -33119,7 +33119,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -33669,7 +33669,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -34219,7 +34219,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -34769,7 +34769,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -35319,7 +35319,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -36163,16 +36163,16 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O197" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q197" t="n">
         <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>0.02325563908550455</v>
+        <v>0.03682142855204888</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -36707,16 +36707,16 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O200" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q200" t="n">
         <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>0.01738276978574758</v>
+        <v>0.02172846223218448</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
@@ -36869,10 +36869,10 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U201" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -37616,7 +37616,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10745</v>
+        <v>10754</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -34363,16 +34363,16 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O185" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q185" t="n">
         <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>0.2129389298754079</v>
+        <v>0.208593237428971</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
@@ -34525,10 +34525,10 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O186" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U186" t="inlineStr">
         <is>
@@ -37651,16 +37651,16 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="O203" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Q203" t="n">
         <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>0.0465112781710091</v>
+        <v>0.06976691725651366</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -38195,16 +38195,16 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O206" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q206" t="n">
         <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>0.02172846223218448</v>
+        <v>0.03041984712505827</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -38357,10 +38357,10 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O207" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U207" t="inlineStr">
         <is>
@@ -38923,6 +38923,154 @@
       <c r="BC209" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>14</v>
+      </c>
+      <c r="O210" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0.01143531770592073</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr"/>
+      <c r="AT210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA210" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB210" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC210" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38959,7 +39107,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -39042,7 +39190,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
@@ -39052,7 +39200,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -39104,7 +39252,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10760</v>
+        <v>10787</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>16</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>4</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.04440596913918363</v>
       </c>
@@ -1616,9 +1610,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2012,9 +2003,6 @@
       <c r="O9" t="n">
         <v>15</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.2032905420295064</v>
       </c>
@@ -2160,9 +2148,6 @@
       <c r="O10" t="n">
         <v>98</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.1899210525316205</v>
       </c>
@@ -2308,9 +2293,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2953,7 +2935,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3100,9 +3082,6 @@
       <c r="O15" t="n">
         <v>5</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.04672440214141673</v>
       </c>
@@ -3745,7 +3724,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4043,9 +4022,6 @@
       <c r="P20" t="n">
         <v>10</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.002865038132769385</v>
       </c>
@@ -4593,9 +4569,6 @@
       <c r="P23" t="n">
         <v>7</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.00200552669293857</v>
       </c>
@@ -5143,9 +5116,6 @@
       <c r="P26" t="n">
         <v>7</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.00200552669293857</v>
       </c>
@@ -5693,9 +5663,6 @@
       <c r="P29" t="n">
         <v>10</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.002865038132769385</v>
       </c>
@@ -6240,9 +6207,6 @@
       <c r="O32" t="n">
         <v>10</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6633,9 +6597,6 @@
       <c r="O34" t="n">
         <v>7</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.07771044599357135</v>
       </c>
@@ -6943,9 +6904,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -7339,9 +7297,6 @@
       <c r="O38" t="n">
         <v>7</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.09486891961376966</v>
       </c>
@@ -7487,9 +7442,6 @@
       <c r="O39" t="n">
         <v>105</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.2034868419981648</v>
       </c>
@@ -7635,9 +7587,6 @@
       <c r="O40" t="n">
         <v>6</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.1061385495477304</v>
       </c>
@@ -8280,7 +8229,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -8427,9 +8376,6 @@
       <c r="O44" t="n">
         <v>12</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.1121385651394002</v>
       </c>
@@ -9072,7 +9018,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -9370,9 +9316,6 @@
       <c r="P49" t="n">
         <v>13</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.003724549572600201</v>
       </c>
@@ -9920,9 +9863,6 @@
       <c r="P52" t="n">
         <v>16</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.004584061012431017</v>
       </c>
@@ -10470,9 +10410,6 @@
       <c r="P55" t="n">
         <v>11</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.003151541946046324</v>
       </c>
@@ -11020,9 +10957,6 @@
       <c r="P58" t="n">
         <v>5</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -11567,9 +11501,6 @@
       <c r="O61" t="n">
         <v>15</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="S61" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11960,9 +11891,6 @@
       <c r="O63" t="n">
         <v>8</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.08881193827836725</v>
       </c>
@@ -12270,9 +12198,6 @@
       <c r="O65" t="n">
         <v>1</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -12666,9 +12591,6 @@
       <c r="O67" t="n">
         <v>8</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.1084216224157367</v>
       </c>
@@ -12814,9 +12736,6 @@
       <c r="O68" t="n">
         <v>176</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.3410827065874001</v>
       </c>
@@ -12962,9 +12881,6 @@
       <c r="O69" t="n">
         <v>4</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.07075903303182025</v>
       </c>
@@ -13607,7 +13523,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -13754,9 +13670,6 @@
       <c r="O73" t="n">
         <v>7</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.06541416299798342</v>
       </c>
@@ -14399,7 +14312,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -14697,9 +14610,6 @@
       <c r="P78" t="n">
         <v>5</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -15247,9 +15157,6 @@
       <c r="P81" t="n">
         <v>9</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.002578534319492447</v>
       </c>
@@ -15797,9 +15704,6 @@
       <c r="P84" t="n">
         <v>2</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -16347,9 +16251,6 @@
       <c r="P87" t="n">
         <v>9</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.002578534319492447</v>
       </c>
@@ -16746,9 +16647,6 @@
       <c r="O89" t="n">
         <v>10</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.0367281181951979</v>
       </c>
@@ -16894,9 +16792,6 @@
       <c r="O90" t="n">
         <v>5</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17287,9 +17182,6 @@
       <c r="O92" t="n">
         <v>2</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.02220298456959181</v>
       </c>
@@ -17597,9 +17489,6 @@
       <c r="O94" t="n">
         <v>5</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.08894045854320688</v>
       </c>
@@ -17993,9 +17882,6 @@
       <c r="O96" t="n">
         <v>4</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -18141,9 +18027,6 @@
       <c r="O97" t="n">
         <v>153</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.296509398340183</v>
       </c>
@@ -18289,9 +18172,6 @@
       <c r="O98" t="n">
         <v>4</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.07075903303182025</v>
       </c>
@@ -18685,9 +18565,6 @@
       <c r="O100" t="n">
         <v>3</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.05673781399415487</v>
       </c>
@@ -18934,7 +18811,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -19081,9 +18958,6 @@
       <c r="O102" t="n">
         <v>5</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.04672440214141673</v>
       </c>
@@ -19477,9 +19351,6 @@
       <c r="O104" t="n">
         <v>86</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.373729550393573</v>
       </c>
@@ -19726,7 +19597,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -20024,9 +19895,6 @@
       <c r="P107" t="n">
         <v>3</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -20574,9 +20442,6 @@
       <c r="P110" t="n">
         <v>7</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.00200552669293857</v>
       </c>
@@ -21124,9 +20989,6 @@
       <c r="P113" t="n">
         <v>6</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -21674,9 +21536,6 @@
       <c r="P116" t="n">
         <v>5</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -22073,9 +21932,6 @@
       <c r="O118" t="n">
         <v>9</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.03305530637567811</v>
       </c>
@@ -22221,9 +22077,6 @@
       <c r="O119" t="n">
         <v>12</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="S119" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22614,9 +22467,6 @@
       <c r="O121" t="n">
         <v>6</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.06660895370877544</v>
       </c>
@@ -22924,9 +22774,6 @@
       <c r="O123" t="n">
         <v>1</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -23320,9 +23167,6 @@
       <c r="O125" t="n">
         <v>5</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.06776351400983546</v>
       </c>
@@ -23468,9 +23312,6 @@
       <c r="O126" t="n">
         <v>179</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.3468966163587762</v>
       </c>
@@ -23616,9 +23457,6 @@
       <c r="O127" t="n">
         <v>3</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.05306927477386519</v>
       </c>
@@ -24012,9 +23850,6 @@
       <c r="O129" t="n">
         <v>4</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.07565041865887316</v>
       </c>
@@ -24261,7 +24096,7 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -24408,9 +24243,6 @@
       <c r="O131" t="n">
         <v>6</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.05606928256970008</v>
       </c>
@@ -24804,9 +24636,6 @@
       <c r="O133" t="n">
         <v>77</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.334618318375641</v>
       </c>
@@ -25053,7 +24882,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -25351,9 +25180,6 @@
       <c r="P136" t="n">
         <v>9</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.002578534319492447</v>
       </c>
@@ -25901,9 +25727,6 @@
       <c r="P139" t="n">
         <v>9</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.002578534319492447</v>
       </c>
@@ -26451,9 +26274,6 @@
       <c r="P142" t="n">
         <v>5</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -27001,9 +26821,6 @@
       <c r="P145" t="n">
         <v>3</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -27551,9 +27368,6 @@
       <c r="P148" t="n">
         <v>4</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -27950,9 +27764,6 @@
       <c r="O150" t="n">
         <v>6</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.02203687091711874</v>
       </c>
@@ -28098,9 +27909,6 @@
       <c r="O151" t="n">
         <v>5</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.05550746142397953</v>
       </c>
@@ -28408,9 +28216,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -28804,9 +28609,6 @@
       <c r="O155" t="n">
         <v>5</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.06776351400983546</v>
       </c>
@@ -28952,9 +28754,6 @@
       <c r="O156" t="n">
         <v>198</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.3837180449108251</v>
       </c>
@@ -29100,9 +28899,6 @@
       <c r="O157" t="n">
         <v>6</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.1061385495477304</v>
       </c>
@@ -29496,9 +29292,6 @@
       <c r="O159" t="n">
         <v>3</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.05673781399415487</v>
       </c>
@@ -29745,7 +29538,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -29892,9 +29685,6 @@
       <c r="O161" t="n">
         <v>2</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -30288,9 +30078,6 @@
       <c r="O163" t="n">
         <v>58</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.25205016189334</v>
       </c>
@@ -30537,7 +30324,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -30684,9 +30471,6 @@
       <c r="O165" t="n">
         <v>5</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.004084042037828832</v>
       </c>
@@ -30835,9 +30619,6 @@
       <c r="P166" t="n">
         <v>4</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -31234,9 +31015,6 @@
       <c r="O168" t="n">
         <v>3</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.002450425222697299</v>
       </c>
@@ -31385,9 +31163,6 @@
       <c r="P169" t="n">
         <v>6</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -31784,9 +31559,6 @@
       <c r="O171" t="n">
         <v>2</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -31935,9 +31707,6 @@
       <c r="P172" t="n">
         <v>9</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.002578534319492447</v>
       </c>
@@ -32334,9 +32103,6 @@
       <c r="O174" t="n">
         <v>6</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.004900850445394598</v>
       </c>
@@ -32485,9 +32251,6 @@
       <c r="P175" t="n">
         <v>5</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -32884,9 +32647,6 @@
       <c r="O177" t="n">
         <v>6</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.02203687091711874</v>
       </c>
@@ -33032,9 +32792,6 @@
       <c r="O178" t="n">
         <v>1</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -33428,9 +33185,6 @@
       <c r="O180" t="n">
         <v>143</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.2771296991022626</v>
       </c>
@@ -33576,9 +33330,6 @@
       <c r="O181" t="n">
         <v>8</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.1415180660636405</v>
       </c>
@@ -33972,9 +33723,6 @@
       <c r="O183" t="n">
         <v>3</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.02803464128485004</v>
       </c>
@@ -34363,16 +34111,13 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O185" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q185" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="R185" t="n">
-        <v>0.208593237428971</v>
+        <v>0.2129389298754079</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
@@ -34525,10 +34270,10 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O186" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U186" t="inlineStr">
         <is>
@@ -34617,7 +34362,7 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN186" t="b">
@@ -34764,9 +34509,6 @@
       <c r="O187" t="n">
         <v>9</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.007351275668091897</v>
       </c>
@@ -34915,9 +34657,6 @@
       <c r="P188" t="n">
         <v>3</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -35314,9 +35053,6 @@
       <c r="O190" t="n">
         <v>11</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.00898489248322343</v>
       </c>
@@ -35465,9 +35201,6 @@
       <c r="P191" t="n">
         <v>5</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -35864,9 +35597,6 @@
       <c r="O193" t="n">
         <v>13</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.01061850929835496</v>
       </c>
@@ -36015,9 +35745,6 @@
       <c r="P194" t="n">
         <v>5</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -36414,9 +36141,6 @@
       <c r="O196" t="n">
         <v>8</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.00653446726052613</v>
       </c>
@@ -36565,9 +36289,6 @@
       <c r="P197" t="n">
         <v>5</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -36964,9 +36685,6 @@
       <c r="O199" t="n">
         <v>16</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.01306893452105226</v>
       </c>
@@ -37112,9 +36830,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -37260,9 +36975,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -37656,9 +37368,6 @@
       <c r="O203" t="n">
         <v>36</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.06976691725651366</v>
       </c>
@@ -37799,16 +37508,13 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O204" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
@@ -37961,10 +37667,10 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U205" t="inlineStr">
         <is>
@@ -38200,9 +37906,6 @@
       <c r="O206" t="n">
         <v>7</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.03041984712505827</v>
       </c>
@@ -38449,7 +38152,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -38599,9 +38302,6 @@
       <c r="P208" t="n">
         <v>2</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -38998,9 +38698,6 @@
       <c r="O210" t="n">
         <v>14</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.01143531770592073</v>
       </c>
@@ -39071,6 +38768,405 @@
       <c r="BC210" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>6</v>
+      </c>
+      <c r="O211" t="n">
+        <v>6</v>
+      </c>
+      <c r="P211" t="n">
+        <v>6</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0.001719022879661631</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>6</v>
+      </c>
+      <c r="O212" t="n">
+        <v>6</v>
+      </c>
+      <c r="P212" t="n">
+        <v>6</v>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN212" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39107,7 +39203,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -39190,7 +39286,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10">
@@ -39200,7 +39296,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -39220,7 +39316,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -39252,7 +39348,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10787</v>
+        <v>10796</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -27904,13 +27904,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O151" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R151" t="n">
-        <v>0.05550746142397953</v>
+        <v>0.07771044599357135</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -32748,12 +32748,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -32787,95 +32787,81 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O178" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R178" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.07771044599357135</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -32902,7 +32888,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -32951,98 +32937,23 @@
       <c r="O179" t="n">
         <v>1</v>
       </c>
+      <c r="R179" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U179" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_115</t>
         </is>
       </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE179" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF179" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG179" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN179" t="b">
-        <v>1</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
@@ -33136,17 +33047,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -33180,81 +33091,170 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="O180" t="n">
-        <v>143</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0.2771296991022626</v>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN180" t="b">
+        <v>1</v>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
       <c r="AT180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -33286,12 +33286,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -33325,95 +33325,81 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="O181" t="n">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="R181" t="n">
-        <v>0.1415180660636405</v>
+        <v>0.2771296991022626</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -33440,7 +33426,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -33489,98 +33475,23 @@
       <c r="O182" t="n">
         <v>8</v>
       </c>
+      <c r="R182" t="n">
+        <v>0.1415180660636405</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U182" t="inlineStr">
         <is>
           <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
-      <c r="V182" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W182" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>Hepatitt A</t>
-        </is>
-      </c>
-      <c r="Y182" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD182" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE182" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF182" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG182" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH182" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ182" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK182" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM182" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN182" t="b">
-        <v>1</v>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
@@ -33674,17 +33585,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -33718,22 +33629,39 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O183" t="n">
-        <v>3</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0.02803464128485004</v>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>Hepatitt A</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -33741,6 +33669,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN183" t="b">
+        <v>1</v>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33758,7 +33744,7 @@
       </c>
       <c r="AS183" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT183" t="n">
@@ -33771,42 +33757,42 @@
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33833,7 +33819,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -33882,98 +33868,23 @@
       <c r="O184" t="n">
         <v>3</v>
       </c>
+      <c r="R184" t="n">
+        <v>0.02803464128485004</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U184" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
-      <c r="V184" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W184" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X184" t="inlineStr">
-        <is>
-          <t>Hepatit A</t>
-        </is>
-      </c>
-      <c r="Y184" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD184" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE184" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF184" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG184" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN184" t="b">
-        <v>1</v>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
@@ -34067,17 +33978,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -34111,22 +34022,39 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="O185" t="n">
-        <v>49</v>
-      </c>
-      <c r="R185" t="n">
-        <v>0.2129389298754079</v>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>Hepatit A</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -34134,6 +34062,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN185" t="b">
+        <v>1</v>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -34151,7 +34137,7 @@
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT185" t="n">
@@ -34164,42 +34150,42 @@
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34226,7 +34212,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -34275,98 +34261,23 @@
       <c r="O186" t="n">
         <v>49</v>
       </c>
+      <c r="R186" t="n">
+        <v>0.2129389298754079</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U186" t="inlineStr">
         <is>
           <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
-        </is>
-      </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>急性病毒性Ａ型肝炎</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF186" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN186" t="b">
-        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
@@ -34460,17 +34371,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -34495,7 +34406,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -34504,81 +34415,170 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="O187" t="n">
-        <v>9</v>
-      </c>
-      <c r="R187" t="n">
-        <v>0.007351275668091897</v>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>49</v>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>急性病毒性Ａ型肝炎</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN187" t="b">
+        <v>1</v>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
       <c r="AT187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -34610,12 +34610,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -34649,98 +34649,81 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O188" t="n">
-        <v>3</v>
-      </c>
-      <c r="P188" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R188" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="AA188" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ188" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34767,7 +34750,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -34819,98 +34802,23 @@
       <c r="P189" t="n">
         <v>3</v>
       </c>
+      <c r="R189" t="n">
+        <v>0.0008595114398308156</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U189" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V189" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W189" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y189" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD189" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE189" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF189" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG189" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN189" t="b">
-        <v>1</v>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
@@ -35004,17 +34912,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -35039,7 +34947,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -35048,81 +34956,173 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O190" t="n">
-        <v>11</v>
-      </c>
-      <c r="R190" t="n">
-        <v>0.00898489248322343</v>
-      </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P190" t="n">
+        <v>3</v>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN190" t="b">
+        <v>1</v>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35154,12 +35154,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -35193,98 +35193,81 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O191" t="n">
-        <v>5</v>
-      </c>
-      <c r="P191" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R191" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="AA191" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35311,7 +35294,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -35363,98 +35346,23 @@
       <c r="P192" t="n">
         <v>5</v>
       </c>
+      <c r="R192" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U192" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN192" t="b">
-        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
@@ -35548,17 +35456,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -35583,7 +35491,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -35592,81 +35500,173 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O193" t="n">
-        <v>13</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0.01061850929835496</v>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="P193" t="n">
+        <v>5</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
+        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35698,12 +35698,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -35737,98 +35737,81 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O194" t="n">
-        <v>5</v>
-      </c>
-      <c r="P194" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="R194" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.01061850929835496</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="AA194" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ194" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35855,7 +35838,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -35907,98 +35890,23 @@
       <c r="P195" t="n">
         <v>5</v>
       </c>
+      <c r="R195" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U195" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD195" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE195" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG195" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN195" t="b">
-        <v>1</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
@@ -36092,17 +36000,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -36127,7 +36035,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -36136,81 +36044,173 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O196" t="n">
-        <v>8</v>
-      </c>
-      <c r="R196" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="P196" t="n">
+        <v>5</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN196" t="b">
+        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36242,12 +36242,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -36281,98 +36281,81 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O197" t="n">
-        <v>5</v>
-      </c>
-      <c r="P197" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R197" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="AA197" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr"/>
       <c r="AT197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36399,7 +36382,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -36451,98 +36434,23 @@
       <c r="P198" t="n">
         <v>5</v>
       </c>
+      <c r="R198" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U198" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN198" t="b">
-        <v>1</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
@@ -36636,17 +36544,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -36671,7 +36579,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -36680,81 +36588,173 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O199" t="n">
-        <v>16</v>
-      </c>
-      <c r="R199" t="n">
-        <v>0.01306893452105226</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="P199" t="n">
+        <v>5</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36786,12 +36786,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -36816,22 +36816,22 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O200" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>0.01306893452105226</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
@@ -36864,42 +36864,42 @@
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36931,12 +36931,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -36983,82 +36983,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -37085,7 +37071,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -37134,98 +37120,23 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_115</t>
         </is>
       </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG202" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN202" t="b">
-        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
@@ -37319,17 +37230,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -37363,81 +37274,170 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
-        <v>36</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0.06976691725651366</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
       <c r="AT203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -37469,12 +37469,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -37508,95 +37508,81 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="O204" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="R204" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.06976691725651366</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -37623,7 +37609,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -37672,98 +37658,23 @@
       <c r="O205" t="n">
         <v>2</v>
       </c>
+      <c r="R205" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U205" t="inlineStr">
         <is>
           <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>Hepatitt A</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN205" t="b">
-        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -37857,17 +37768,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -37901,22 +37812,39 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O206" t="n">
-        <v>7</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0.03041984712505827</v>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Hepatitt A</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -37924,6 +37852,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN206" t="b">
+        <v>1</v>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -37941,7 +37927,7 @@
       </c>
       <c r="AS206" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT206" t="n">
@@ -37954,42 +37940,42 @@
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -38016,7 +38002,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -38065,98 +38051,23 @@
       <c r="O207" t="n">
         <v>7</v>
       </c>
+      <c r="R207" t="n">
+        <v>0.03041984712505827</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U207" t="inlineStr">
         <is>
           <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
-        </is>
-      </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>急性病毒性Ａ型肝炎</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD207" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE207" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF207" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG207" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ207" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK207" t="inlineStr">
-        <is>
-          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
-        </is>
-      </c>
-      <c r="AM207" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN207" t="b">
-        <v>1</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
@@ -38250,17 +38161,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -38294,35 +38205,107 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O208" t="n">
-        <v>2</v>
-      </c>
-      <c r="P208" t="n">
-        <v>2</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>急性病毒性Ａ型肝炎</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN208" t="b">
+        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
@@ -38332,12 +38315,12 @@
       </c>
       <c r="AQ208" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT208" t="n">
@@ -38345,47 +38328,47 @@
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -38412,7 +38395,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -38464,98 +38447,23 @@
       <c r="P209" t="n">
         <v>2</v>
       </c>
+      <c r="R209" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U209" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN209" t="b">
-        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
@@ -38649,17 +38557,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -38684,7 +38592,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -38693,81 +38601,173 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O210" t="n">
-        <v>14</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0.01143531770592073</v>
-      </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P210" t="n">
+        <v>2</v>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN210" t="b">
+        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38799,12 +38799,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -38829,7 +38829,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -38838,98 +38838,81 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O211" t="n">
-        <v>6</v>
-      </c>
-      <c r="P211" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="R211" t="n">
-        <v>0.001719022879661631</v>
+        <v>0.01143531770592073</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="AA211" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ211" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38956,7 +38939,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -39008,98 +38991,23 @@
       <c r="P212" t="n">
         <v>6</v>
       </c>
+      <c r="R212" t="n">
+        <v>0.001719022879661631</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U212" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD212" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE212" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF212" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN212" t="b">
-        <v>1</v>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
@@ -39165,6 +39073,243 @@
         </is>
       </c>
       <c r="BC212" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>6</v>
+      </c>
+      <c r="O213" t="n">
+        <v>6</v>
+      </c>
+      <c r="P213" t="n">
+        <v>6</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN213" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -39286,7 +39431,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -39296,7 +39441,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -39348,7 +39493,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10796</v>
+        <v>10805</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -28749,13 +28749,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O156" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="R156" t="n">
-        <v>0.3837180449108251</v>
+        <v>0.3856560148346171</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -37508,13 +37508,13 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="O204" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="R204" t="n">
-        <v>0.06976691725651366</v>
+        <v>0.09689849618960229</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
@@ -38046,13 +38046,13 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O207" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R207" t="n">
-        <v>0.03041984712505827</v>
+        <v>0.03476553957149517</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -38205,10 +38205,10 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O208" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U208" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10805</v>
+        <v>10821</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -38046,13 +38046,13 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O207" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R207" t="n">
-        <v>0.03476553957149517</v>
+        <v>0.03911123201793206</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -38205,10 +38205,10 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O208" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U208" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10821</v>
+        <v>10822</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -38436,13 +38436,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O209" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R209" t="n">
-        <v>0.03911123201793206</v>
+        <v>0.05649400180367965</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -38595,10 +38595,10 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O210" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U210" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10829</v>
+        <v>10833</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -37505,13 +37505,13 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
@@ -37664,10 +37664,10 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U205" t="inlineStr">
         <is>
@@ -37898,13 +37898,13 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="O206" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="R206" t="n">
-        <v>0.09689849618960229</v>
+        <v>0.1085263157323546</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -39702,6 +39702,151 @@
       <c r="BC215" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>11</v>
+      </c>
+      <c r="O216" t="n">
+        <v>11</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO216" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP216" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr"/>
+      <c r="AT216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV216" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39738,7 +39883,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -39821,7 +39966,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
@@ -39831,7 +39976,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -39883,7 +40028,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10833</v>
+        <v>10851</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -33283,12 +33283,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -33322,13 +33322,16 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>1</v>
+        <v>1638</v>
       </c>
       <c r="O181" t="n">
-        <v>1</v>
+        <v>1638</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.1159306155506567</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -33337,7 +33340,7 @@
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_115</t>
+          <t>SER_CN_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -33347,7 +33350,7 @@
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
@@ -33357,12 +33360,12 @@
       </c>
       <c r="AQ181" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_115</t>
+          <t>SER_CN_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT181" t="n">
@@ -33370,47 +33373,47 @@
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -33442,12 +33445,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -33481,29 +33484,29 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>1</v>
+        <v>1638</v>
       </c>
       <c r="O182" t="n">
-        <v>1</v>
+        <v>1638</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_115</t>
+          <t>SER_CN_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_115</t>
+          <t>SER_CN_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="Y182" t="inlineStr">
@@ -33513,7 +33516,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -33528,7 +33531,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr">
@@ -33543,7 +33546,7 @@
       </c>
       <c r="AF182" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG182" t="inlineStr">
@@ -33563,17 +33566,17 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
+          <t>China CDC source-reported hepatitis A component.</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -33581,7 +33584,7 @@
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
@@ -33591,12 +33594,12 @@
       </c>
       <c r="AQ182" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_115</t>
+          <t>SER_CN_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT182" t="n">
@@ -33604,47 +33607,47 @@
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -33676,12 +33679,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -33715,81 +33718,95 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="O183" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="R183" t="n">
-        <v>0.2771296991022626</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
       <c r="AT183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -33816,17 +33833,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -33860,22 +33877,39 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O184" t="n">
-        <v>8</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0.1415180660636405</v>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -33883,6 +33917,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN184" t="b">
+        <v>1</v>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33895,12 +33987,12 @@
       </c>
       <c r="AQ184" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
+          <t>SER_FI_THL_TTR_115</t>
         </is>
       </c>
       <c r="AT184" t="n">
@@ -33908,47 +34000,47 @@
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -33975,17 +34067,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -34019,170 +34111,81 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="O185" t="n">
-        <v>8</v>
-      </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W185" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X185" t="inlineStr">
-        <is>
-          <t>Hepatitt A</t>
-        </is>
-      </c>
-      <c r="Y185" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA185" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD185" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE185" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF185" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG185" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN185" t="b">
-        <v>1</v>
+        <v>143</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0.2771296991022626</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ185" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -34214,12 +34217,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -34253,13 +34256,13 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O186" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R186" t="n">
-        <v>0.02803464128485004</v>
+        <v>0.1415180660636405</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -34268,7 +34271,7 @@
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -34293,7 +34296,7 @@
       </c>
       <c r="AS186" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT186" t="n">
@@ -34306,42 +34309,42 @@
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -34373,12 +34376,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -34412,29 +34415,29 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O187" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>Hepatit A</t>
+          <t>Hepatitt A</t>
         </is>
       </c>
       <c r="Y187" t="inlineStr">
@@ -34459,7 +34462,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr">
@@ -34494,17 +34497,17 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -34527,7 +34530,7 @@
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT187" t="n">
@@ -34540,42 +34543,42 @@
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -34607,12 +34610,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -34646,13 +34649,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="O188" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="R188" t="n">
-        <v>0.2129389298754079</v>
+        <v>0.02803464128485004</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -34661,7 +34664,7 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -34686,7 +34689,7 @@
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT188" t="n">
@@ -34699,42 +34702,42 @@
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34766,12 +34769,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -34805,29 +34808,29 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="O189" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>急性病毒性Ａ型肝炎</t>
+          <t>Hepatit A</t>
         </is>
       </c>
       <c r="Y189" t="inlineStr">
@@ -34837,7 +34840,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -34852,7 +34855,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr">
@@ -34867,7 +34870,7 @@
       </c>
       <c r="AF189" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG189" t="inlineStr">
@@ -34887,17 +34890,17 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
         </is>
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -34920,7 +34923,7 @@
       </c>
       <c r="AS189" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT189" t="n">
@@ -34933,42 +34936,42 @@
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35000,12 +35003,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -35030,7 +35033,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -35039,81 +35042,95 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="O190" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="R190" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.2129389298754079</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -35140,17 +35157,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -35175,7 +35192,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -35184,35 +35201,107 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="O191" t="n">
-        <v>3</v>
-      </c>
-      <c r="P191" t="n">
-        <v>3</v>
-      </c>
-      <c r="R191" t="n">
-        <v>0.0008595114398308156</v>
-      </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>49</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>急性病毒性Ａ型肝炎</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN191" t="b">
+        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
@@ -35222,12 +35311,12 @@
       </c>
       <c r="AQ191" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT191" t="n">
@@ -35235,47 +35324,47 @@
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -35302,17 +35391,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -35346,173 +35435,81 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O192" t="n">
-        <v>3</v>
-      </c>
-      <c r="P192" t="n">
-        <v>3</v>
-      </c>
-      <c r="U192" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA192" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN192" t="b">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35544,12 +35541,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -35574,7 +35571,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -35583,81 +35580,98 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O193" t="n">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="P193" t="n">
+        <v>3</v>
       </c>
       <c r="R193" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35684,7 +35698,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -35719,7 +35733,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -35728,31 +35742,106 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O194" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P194" t="n">
-        <v>5</v>
-      </c>
-      <c r="R194" t="n">
-        <v>0.001432519066384693</v>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U194" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN194" t="b">
+        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
@@ -35846,17 +35935,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -35890,173 +35979,81 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O195" t="n">
-        <v>5</v>
-      </c>
-      <c r="P195" t="n">
-        <v>5</v>
-      </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD195" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE195" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG195" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN195" t="b">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="R195" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36088,12 +36085,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -36118,7 +36115,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -36127,81 +36124,98 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O196" t="n">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="P196" t="n">
+        <v>5</v>
       </c>
       <c r="R196" t="n">
-        <v>0.01061850929835496</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36228,7 +36242,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -36263,7 +36277,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -36280,23 +36294,98 @@
       <c r="P197" t="n">
         <v>5</v>
       </c>
-      <c r="R197" t="n">
-        <v>0.001432519066384693</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U197" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
@@ -36390,17 +36479,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -36434,173 +36523,81 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O198" t="n">
-        <v>5</v>
-      </c>
-      <c r="P198" t="n">
-        <v>5</v>
-      </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN198" t="b">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0.01061850929835496</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36632,12 +36629,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -36662,7 +36659,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -36671,81 +36668,98 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O199" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="P199" t="n">
+        <v>5</v>
       </c>
       <c r="R199" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36772,7 +36786,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -36807,7 +36821,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -36824,23 +36838,98 @@
       <c r="P200" t="n">
         <v>5</v>
       </c>
-      <c r="R200" t="n">
-        <v>0.001432519066384693</v>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U200" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN200" t="b">
+        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
@@ -36934,17 +37023,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -36978,173 +37067,81 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O201" t="n">
-        <v>5</v>
-      </c>
-      <c r="P201" t="n">
-        <v>5</v>
-      </c>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN201" t="b">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37176,12 +37173,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -37206,7 +37203,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -37215,81 +37212,98 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O202" t="n">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="P202" t="n">
+        <v>5</v>
       </c>
       <c r="R202" t="n">
-        <v>0.01306893452105226</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37316,17 +37330,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -37351,90 +37365,182 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O203" t="n">
-        <v>0</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="P203" t="n">
+        <v>5</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37466,12 +37572,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -37496,104 +37602,90 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N204" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O204" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="R204" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.01306893452105226</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37620,17 +37712,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -37664,170 +37756,81 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
-        <v>1</v>
-      </c>
-      <c r="U205" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA205" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R205" t="n">
+        <v>0</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP205" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
+      <c r="AT205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV205" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN205" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO205" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP205" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AT205" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU205" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV205" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -37859,12 +37862,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -37898,81 +37901,95 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="O206" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="R206" t="n">
-        <v>0.1085263157323546</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -37999,17 +38016,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -38043,22 +38060,39 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O207" t="n">
-        <v>2</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0.03537951651591013</v>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -38066,6 +38100,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -38078,12 +38170,12 @@
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
+          <t>SER_FI_THL_TTR_115</t>
         </is>
       </c>
       <c r="AT207" t="n">
@@ -38091,47 +38183,47 @@
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -38158,17 +38250,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -38202,170 +38294,81 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="O208" t="n">
-        <v>2</v>
-      </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>Hepatitt A</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN208" t="b">
-        <v>1</v>
+        <v>56</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0.1085263157323546</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -38397,12 +38400,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -38436,13 +38439,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O209" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="R209" t="n">
-        <v>0.05649400180367965</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -38451,7 +38454,7 @@
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -38476,7 +38479,7 @@
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT209" t="n">
@@ -38489,42 +38492,42 @@
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -38556,12 +38559,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -38595,29 +38598,29 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O210" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t>急性病毒性Ａ型肝炎</t>
+          <t>Hepatitt A</t>
         </is>
       </c>
       <c r="Y210" t="inlineStr">
@@ -38627,7 +38630,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -38642,7 +38645,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -38657,7 +38660,7 @@
       </c>
       <c r="AF210" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG210" t="inlineStr">
@@ -38677,17 +38680,17 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
         <is>
-          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -38710,7 +38713,7 @@
       </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT210" t="n">
@@ -38723,42 +38726,42 @@
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -38790,12 +38793,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -38829,16 +38832,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O211" t="n">
-        <v>2</v>
-      </c>
-      <c r="P211" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="R211" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.05649400180367965</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -38847,17 +38847,17 @@
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
@@ -38867,12 +38867,12 @@
       </c>
       <c r="AQ211" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT211" t="n">
@@ -38880,47 +38880,47 @@
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -38952,12 +38952,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -38991,32 +38991,29 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O212" t="n">
-        <v>2</v>
-      </c>
-      <c r="P212" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>急性病毒性Ａ型肝炎</t>
         </is>
       </c>
       <c r="Y212" t="inlineStr">
@@ -39031,7 +39028,7 @@
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
@@ -39041,7 +39038,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -39081,12 +39078,12 @@
       </c>
       <c r="AK212" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -39094,7 +39091,7 @@
       </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
@@ -39104,12 +39101,12 @@
       </c>
       <c r="AQ212" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT212" t="n">
@@ -39117,47 +39114,47 @@
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -39189,12 +39186,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -39219,7 +39216,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -39228,81 +39225,98 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O213" t="n">
-        <v>14</v>
+        <v>2</v>
+      </c>
+      <c r="P213" t="n">
+        <v>2</v>
       </c>
       <c r="R213" t="n">
-        <v>0.01143531770592073</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39329,7 +39343,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -39364,7 +39378,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -39373,31 +39387,106 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O214" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P214" t="n">
-        <v>6</v>
-      </c>
-      <c r="R214" t="n">
-        <v>0.001719022879661631</v>
-      </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U214" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN214" t="b">
+        <v>1</v>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
@@ -39491,17 +39580,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -39526,7 +39615,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -39535,173 +39624,81 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O215" t="n">
-        <v>6</v>
-      </c>
-      <c r="P215" t="n">
-        <v>6</v>
-      </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="V215" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W215" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X215" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y215" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z215" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA215" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB215" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD215" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE215" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF215" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG215" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM215" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN215" t="b">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0.01143531770592073</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ215" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39733,118 +39730,517 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>6</v>
+      </c>
+      <c r="O216" t="n">
+        <v>6</v>
+      </c>
+      <c r="P216" t="n">
+        <v>6</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0.001719022879661631</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO216" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP216" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV216" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>6</v>
+      </c>
+      <c r="O217" t="n">
+        <v>6</v>
+      </c>
+      <c r="P217" t="n">
+        <v>6</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN217" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV217" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA217" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB217" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC217" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
+      <c r="G218" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>D007</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
         <is>
           <t>甲型肝炎</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
+      <c r="K218" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
+      <c r="L218" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr">
+      <c r="M218" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N216" t="n">
+      <c r="N218" t="n">
         <v>11</v>
       </c>
-      <c r="O216" t="n">
+      <c r="O218" t="n">
         <v>11</v>
       </c>
-      <c r="R216" t="n">
+      <c r="R218" t="n">
         <v>0.00898489248322343</v>
       </c>
-      <c r="S216" t="inlineStr">
+      <c r="S218" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO216" t="inlineStr">
+      <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP216" t="inlineStr">
+      <c r="AP218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR216" t="inlineStr">
+      <c r="AR218" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS216" t="inlineStr"/>
-      <c r="AT216" t="n">
+      <c r="AS218" t="inlineStr"/>
+      <c r="AT218" t="n">
         <v>0</v>
       </c>
-      <c r="AU216" t="inlineStr">
+      <c r="AU218" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV216" t="inlineStr">
+      <c r="AV218" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW216" t="inlineStr">
+      <c r="AW218" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX216" t="inlineStr">
+      <c r="AX218" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY216" t="inlineStr">
+      <c r="AY218" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ216" t="inlineStr">
+      <c r="AZ218" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA216" t="inlineStr">
+      <c r="BA218" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB216" t="inlineStr">
+      <c r="BB218" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC216" t="inlineStr">
+      <c r="BC218" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -39966,7 +40362,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10">
@@ -39976,7 +40372,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -39996,7 +40392,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -40006,7 +40402,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -40028,7 +40424,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10851</v>
+        <v>12489</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -38439,13 +38439,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R209" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -38598,10 +38598,10 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U210" t="inlineStr">
         <is>
@@ -40243,6 +40243,405 @@
       <c r="BC218" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>9</v>
+      </c>
+      <c r="O219" t="n">
+        <v>9</v>
+      </c>
+      <c r="P219" t="n">
+        <v>9</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0.002578534319492447</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>9</v>
+      </c>
+      <c r="O220" t="n">
+        <v>9</v>
+      </c>
+      <c r="P220" t="n">
+        <v>9</v>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM220" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN220" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40279,7 +40678,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -40362,7 +40761,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10">
@@ -40372,7 +40771,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11">
@@ -40392,7 +40791,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -40424,7 +40823,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12489</v>
+        <v>12499</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -34610,12 +34610,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -34649,13 +34649,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O188" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R188" t="n">
-        <v>0.02803464128485004</v>
+        <v>0.132388232653028</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
         </is>
       </c>
       <c r="AT188" t="n">
@@ -34702,42 +34702,42 @@
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34769,12 +34769,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -34808,29 +34808,29 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O189" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
         </is>
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>Hepatit A</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="Y189" t="inlineStr">
@@ -34840,7 +34840,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -34855,7 +34855,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr">
@@ -34890,17 +34890,17 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly hepatitis A notifications.</t>
         </is>
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -34923,7 +34923,7 @@
       </c>
       <c r="AS189" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
         </is>
       </c>
       <c r="AT189" t="n">
@@ -34936,42 +34936,42 @@
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35003,12 +35003,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -35042,13 +35042,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="O190" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="R190" t="n">
-        <v>0.2129389298754079</v>
+        <v>0.02803464128485004</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -35082,7 +35082,7 @@
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT190" t="n">
@@ -35095,42 +35095,42 @@
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35162,12 +35162,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -35201,29 +35201,29 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="O191" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>急性病毒性Ａ型肝炎</t>
+          <t>Hepatit A</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
@@ -35233,7 +35233,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -35248,7 +35248,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr">
@@ -35263,7 +35263,7 @@
       </c>
       <c r="AF191" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG191" t="inlineStr">
@@ -35283,17 +35283,17 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -35316,7 +35316,7 @@
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT191" t="n">
@@ -35329,42 +35329,42 @@
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35396,12 +35396,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -35426,7 +35426,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -35435,81 +35435,95 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="O192" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="R192" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.2129389298754079</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
       <c r="AT192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -35536,17 +35550,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -35571,7 +35585,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -35580,35 +35594,107 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="O193" t="n">
-        <v>3</v>
-      </c>
-      <c r="P193" t="n">
-        <v>3</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0.0008595114398308156</v>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>49</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>急性病毒性Ａ型肝炎</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
+        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
@@ -35618,12 +35704,12 @@
       </c>
       <c r="AQ193" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT193" t="n">
@@ -35631,47 +35717,47 @@
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -35698,17 +35784,17 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -35742,173 +35828,81 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O194" t="n">
-        <v>3</v>
-      </c>
-      <c r="P194" t="n">
-        <v>3</v>
-      </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA194" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN194" t="b">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ194" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35940,12 +35934,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -35970,7 +35964,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -35979,81 +35973,98 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O195" t="n">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="P195" t="n">
+        <v>3</v>
       </c>
       <c r="R195" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36080,7 +36091,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -36115,7 +36126,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -36124,31 +36135,106 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O196" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P196" t="n">
-        <v>5</v>
-      </c>
-      <c r="R196" t="n">
-        <v>0.001432519066384693</v>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U196" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN196" t="b">
+        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -36242,17 +36328,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -36286,173 +36372,81 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O197" t="n">
-        <v>5</v>
-      </c>
-      <c r="P197" t="n">
-        <v>5</v>
-      </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA197" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD197" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE197" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF197" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG197" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN197" t="b">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr"/>
       <c r="AT197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36484,12 +36478,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -36514,7 +36508,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -36523,81 +36517,98 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O198" t="n">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="P198" t="n">
+        <v>5</v>
       </c>
       <c r="R198" t="n">
-        <v>0.01061850929835496</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36624,7 +36635,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -36659,7 +36670,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -36676,23 +36687,98 @@
       <c r="P199" t="n">
         <v>5</v>
       </c>
-      <c r="R199" t="n">
-        <v>0.001432519066384693</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U199" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
@@ -36786,17 +36872,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -36830,173 +36916,81 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O200" t="n">
-        <v>5</v>
-      </c>
-      <c r="P200" t="n">
-        <v>5</v>
-      </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0.01061850929835496</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37028,12 +37022,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -37058,7 +37052,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -37067,81 +37061,98 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O201" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="P201" t="n">
+        <v>5</v>
       </c>
       <c r="R201" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37168,7 +37179,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -37203,7 +37214,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -37220,23 +37231,98 @@
       <c r="P202" t="n">
         <v>5</v>
       </c>
-      <c r="R202" t="n">
-        <v>0.001432519066384693</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
@@ -37330,17 +37416,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -37374,173 +37460,81 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O203" t="n">
-        <v>5</v>
-      </c>
-      <c r="P203" t="n">
-        <v>5</v>
-      </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37572,12 +37566,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -37602,7 +37596,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -37611,81 +37605,98 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O204" t="n">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="P204" t="n">
+        <v>5</v>
       </c>
       <c r="R204" t="n">
-        <v>0.01306893452105226</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37712,17 +37723,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -37747,90 +37758,182 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O205" t="n">
-        <v>0</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="P205" t="n">
+        <v>5</v>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37862,12 +37965,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -37892,104 +37995,90 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N206" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O206" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="R206" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.01306893452105226</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AA206" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38016,17 +38105,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -38060,170 +38149,81 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
-        <v>1</v>
-      </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA207" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD207" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr"/>
+      <c r="AT207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE207" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF207" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG207" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ207" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK207" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
-        </is>
-      </c>
-      <c r="AM207" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN207" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO207" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP207" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AT207" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU207" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV207" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38255,12 +38255,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -38294,81 +38294,95 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="O208" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="R208" t="n">
-        <v>0.1085263157323546</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
       <c r="AT208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -38395,17 +38409,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -38439,22 +38453,39 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O209" t="n">
-        <v>3</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0.05306927477386519</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -38462,6 +38493,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -38474,12 +38563,12 @@
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
+          <t>SER_FI_THL_TTR_115</t>
         </is>
       </c>
       <c r="AT209" t="n">
@@ -38487,47 +38576,47 @@
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -38554,17 +38643,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -38598,170 +38687,81 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="O210" t="n">
-        <v>3</v>
-      </c>
-      <c r="U210" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>Hepatitt A</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA210" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD210" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE210" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF210" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG210" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM210" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN210" t="b">
-        <v>1</v>
+        <v>94</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0.1821691728364523</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ210" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -38793,12 +38793,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -38832,13 +38832,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O211" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R211" t="n">
-        <v>0.05649400180367965</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -38872,7 +38872,7 @@
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT211" t="n">
@@ -38885,42 +38885,42 @@
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -38952,12 +38952,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -38991,29 +38991,29 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O212" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>急性病毒性Ａ型肝炎</t>
+          <t>Hepatitt A</t>
         </is>
       </c>
       <c r="Y212" t="inlineStr">
@@ -39023,7 +39023,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -39038,7 +39038,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -39053,7 +39053,7 @@
       </c>
       <c r="AF212" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG212" t="inlineStr">
@@ -39073,17 +39073,17 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
         <is>
-          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -39106,7 +39106,7 @@
       </c>
       <c r="AS212" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT212" t="n">
@@ -39119,42 +39119,42 @@
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -39186,12 +39186,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -39225,16 +39225,13 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O213" t="n">
-        <v>2</v>
-      </c>
-      <c r="P213" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="R213" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.05649400180367965</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
@@ -39243,17 +39240,17 @@
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
@@ -39263,12 +39260,12 @@
       </c>
       <c r="AQ213" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT213" t="n">
@@ -39276,47 +39273,47 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -39348,12 +39345,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -39387,32 +39384,29 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O214" t="n">
-        <v>2</v>
-      </c>
-      <c r="P214" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="V214" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X214" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>急性病毒性Ａ型肝炎</t>
         </is>
       </c>
       <c r="Y214" t="inlineStr">
@@ -39427,7 +39421,7 @@
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
@@ -39437,7 +39431,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
@@ -39477,12 +39471,12 @@
       </c>
       <c r="AK214" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
         </is>
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -39490,7 +39484,7 @@
       </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
@@ -39500,12 +39494,12 @@
       </c>
       <c r="AQ214" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT214" t="n">
@@ -39513,47 +39507,47 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -39585,12 +39579,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -39615,7 +39609,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -39624,81 +39618,98 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O215" t="n">
-        <v>14</v>
+        <v>2</v>
+      </c>
+      <c r="P215" t="n">
+        <v>2</v>
       </c>
       <c r="R215" t="n">
-        <v>0.01143531770592073</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39725,7 +39736,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -39760,7 +39771,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -39769,31 +39780,106 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O216" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P216" t="n">
-        <v>6</v>
-      </c>
-      <c r="R216" t="n">
-        <v>0.001719022879661631</v>
-      </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM216" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN216" t="b">
+        <v>1</v>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
@@ -39887,17 +39973,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -39922,7 +40008,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -39931,173 +40017,81 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O217" t="n">
-        <v>6</v>
-      </c>
-      <c r="P217" t="n">
-        <v>6</v>
-      </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y217" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA217" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD217" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE217" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF217" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN217" t="b">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0.01143531770592073</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ217" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr"/>
       <c r="AT217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40129,12 +40123,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -40159,7 +40153,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -40168,81 +40162,98 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O218" t="n">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="P218" t="n">
+        <v>6</v>
       </c>
       <c r="R218" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40269,7 +40280,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -40304,7 +40315,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -40313,31 +40324,106 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O219" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P219" t="n">
-        <v>9</v>
-      </c>
-      <c r="R219" t="n">
-        <v>0.002578534319492447</v>
-      </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="U219" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN219" t="b">
+        <v>1</v>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
@@ -40431,217 +40517,669 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>11</v>
+      </c>
+      <c r="O220" t="n">
+        <v>11</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr"/>
+      <c r="AT220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>9</v>
+      </c>
+      <c r="O221" t="n">
+        <v>9</v>
+      </c>
+      <c r="P221" t="n">
+        <v>9</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0.002578534319492447</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU221" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV221" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA221" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB221" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
+      <c r="F222" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
+      <c r="G222" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>D007</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
         <is>
           <t>甲型肝炎</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
+      <c r="K222" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
+      <c r="L222" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr">
+      <c r="M222" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N220" t="n">
+      <c r="N222" t="n">
         <v>9</v>
       </c>
-      <c r="O220" t="n">
+      <c r="O222" t="n">
         <v>9</v>
       </c>
-      <c r="P220" t="n">
+      <c r="P222" t="n">
         <v>9</v>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="U222" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V220" t="inlineStr">
+      <c r="V222" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="W220" t="inlineStr">
+      <c r="W222" t="inlineStr">
         <is>
           <t>SRC_US_NNDSS</t>
         </is>
       </c>
-      <c r="X220" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>Hepatitis A, Confirmed</t>
         </is>
       </c>
-      <c r="Y220" t="inlineStr">
+      <c r="Y222" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z220" t="inlineStr">
+      <c r="Z222" t="inlineStr">
         <is>
           <t>notification</t>
         </is>
       </c>
-      <c r="AA220" t="inlineStr">
+      <c r="AA222" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB220" t="inlineStr">
+      <c r="AB222" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC220" t="inlineStr">
+      <c r="AC222" t="inlineStr">
         <is>
           <t>country:US:national</t>
         </is>
       </c>
-      <c r="AD220" t="inlineStr">
+      <c r="AD222" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE220" t="inlineStr">
+      <c r="AE222" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF220" t="inlineStr">
+      <c r="AF222" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AG220" t="inlineStr">
+      <c r="AG222" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH220" t="inlineStr">
+      <c r="AH222" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI220" t="inlineStr">
+      <c r="AI222" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ220" t="inlineStr">
+      <c r="AJ222" t="inlineStr">
         <is>
           <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
-      <c r="AK220" t="inlineStr">
+      <c r="AK222" t="inlineStr">
         <is>
           <t>Confirmed hepatitis A component reported by NNDSS.</t>
         </is>
       </c>
-      <c r="AM220" t="inlineStr">
+      <c r="AM222" t="inlineStr">
         <is>
           <t>provisional</t>
         </is>
       </c>
-      <c r="AN220" t="b">
+      <c r="AN222" t="b">
         <v>1</v>
       </c>
-      <c r="AO220" t="inlineStr">
+      <c r="AO222" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="AP220" t="inlineStr">
+      <c r="AP222" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ220" t="inlineStr">
+      <c r="AQ222" t="inlineStr">
         <is>
           <t>legacy_gap_fill</t>
         </is>
       </c>
-      <c r="AS220" t="inlineStr">
+      <c r="AS222" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="AT220" t="n">
+      <c r="AT222" t="n">
         <v>1</v>
       </c>
-      <c r="AU220" t="inlineStr">
+      <c r="AU222" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
-      <c r="AV220" t="inlineStr">
+      <c r="AV222" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW220" t="inlineStr">
+      <c r="AW222" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX220" t="inlineStr">
+      <c r="AX222" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY220" t="inlineStr">
+      <c r="AY222" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ220" t="inlineStr">
+      <c r="AZ222" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA220" t="inlineStr">
+      <c r="BA222" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB220" t="inlineStr">
+      <c r="BB222" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC220" t="inlineStr">
+      <c r="BC222" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>8</v>
+      </c>
+      <c r="O223" t="n">
+        <v>8</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr"/>
+      <c r="AT223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU223" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV223" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA223" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB223" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC223" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40678,7 +41216,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -40761,7 +41299,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10">
@@ -40771,7 +41309,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11">
@@ -40791,7 +41329,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -40823,7 +41361,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12499</v>
+        <v>12554</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -38687,13 +38687,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="O210" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="R210" t="n">
-        <v>0.1821691728364523</v>
+        <v>0.1918590224554125</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12554</v>
+        <v>12559</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -3714,7 +3714,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -14348,7 +14348,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -17848,7 +17848,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -18395,7 +18395,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21218,7 +21218,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26197,7 +26197,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27138,7 +27138,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28079,7 +28079,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31570,7 +31570,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32117,7 +32117,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -33058,7 +33058,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -33999,7 +33999,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -34940,7 +34940,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -35881,7 +35881,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39372,7 +39372,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -39916,7 +39916,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -40854,7 +40854,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -41792,7 +41792,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -42730,7 +42730,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -43810,7 +43810,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45920,7 +45920,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -46464,7 +46464,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -47402,7 +47402,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -48340,7 +48340,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -49278,7 +49278,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51286,7 +51286,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -51685,7 +51685,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -52623,7 +52623,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -53561,7 +53561,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -54499,7 +54499,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -3714,7 +3714,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -14348,7 +14348,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -17848,7 +17848,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -18395,7 +18395,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21218,7 +21218,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26197,7 +26197,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27138,7 +27138,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28079,7 +28079,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31570,7 +31570,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32117,7 +32117,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -33058,7 +33058,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -33999,7 +33999,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -34940,7 +34940,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -35881,7 +35881,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39372,7 +39372,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -39916,7 +39916,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -40854,7 +40854,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -41792,7 +41792,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -42730,7 +42730,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -43810,7 +43810,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45920,7 +45920,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -46464,7 +46464,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -47402,7 +47402,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -48340,7 +48340,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -49278,7 +49278,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51286,7 +51286,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -51685,7 +51685,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -52623,7 +52623,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -53561,7 +53561,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -54499,7 +54499,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -44316,12 +44316,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -44355,13 +44355,13 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>143</v>
+        <v>2</v>
       </c>
       <c r="O237" t="n">
-        <v>143</v>
+        <v>2</v>
       </c>
       <c r="R237" t="n">
-        <v>0.2771296991022626</v>
+        <v>0.02710540560393419</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -44394,42 +44394,42 @@
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -44461,12 +44461,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -44500,95 +44500,81 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="O238" t="n">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="R238" t="n">
-        <v>0.1415180660636405</v>
+        <v>0.2771296991022626</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA238" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ238" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr"/>
       <c r="AT238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -44615,7 +44601,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -44664,98 +44650,23 @@
       <c r="O239" t="n">
         <v>8</v>
       </c>
+      <c r="R239" t="n">
+        <v>0.1415180660636405</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U239" t="inlineStr">
         <is>
           <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
-      <c r="V239" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W239" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X239" t="inlineStr">
-        <is>
-          <t>Hepatitt A</t>
-        </is>
-      </c>
-      <c r="Y239" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA239" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD239" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE239" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF239" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG239" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH239" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ239" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK239" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM239" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN239" t="b">
-        <v>1</v>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
@@ -44849,17 +44760,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -44893,22 +44804,39 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O240" t="n">
-        <v>7</v>
-      </c>
-      <c r="R240" t="n">
-        <v>0.132388232653028</v>
-      </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>Hepatitt A</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -44916,6 +44844,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD240" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ240" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK240" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM240" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN240" t="b">
+        <v>1</v>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -44933,7 +44919,7 @@
       </c>
       <c r="AS240" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT240" t="n">
@@ -44946,42 +44932,42 @@
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45008,7 +44994,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -45057,98 +45043,23 @@
       <c r="O241" t="n">
         <v>7</v>
       </c>
+      <c r="R241" t="n">
+        <v>0.132388232653028</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U241" t="inlineStr">
         <is>
           <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
         </is>
       </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly hepatitis A notifications.</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN241" t="b">
-        <v>1</v>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
@@ -45242,17 +45153,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -45286,22 +45197,39 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O242" t="n">
-        <v>3</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0.02803464128485004</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -45309,6 +45237,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly hepatitis A notifications.</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN242" t="b">
+        <v>1</v>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -45326,7 +45312,7 @@
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
         </is>
       </c>
       <c r="AT242" t="n">
@@ -45339,42 +45325,42 @@
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45401,7 +45387,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -45450,98 +45436,23 @@
       <c r="O243" t="n">
         <v>3</v>
       </c>
+      <c r="R243" t="n">
+        <v>0.02803464128485004</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U243" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
-      <c r="V243" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W243" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X243" t="inlineStr">
-        <is>
-          <t>Hepatit A</t>
-        </is>
-      </c>
-      <c r="Y243" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD243" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE243" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF243" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG243" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH243" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI243" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ243" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK243" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM243" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN243" t="b">
-        <v>1</v>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
@@ -45635,17 +45546,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -45679,22 +45590,39 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="O244" t="n">
-        <v>49</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0.2129389298754079</v>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>Hepatit A</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -45702,6 +45630,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN244" t="b">
+        <v>1</v>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -45719,7 +45705,7 @@
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT244" t="n">
@@ -45732,42 +45718,42 @@
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -45794,7 +45780,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -45843,98 +45829,23 @@
       <c r="O245" t="n">
         <v>49</v>
       </c>
+      <c r="R245" t="n">
+        <v>0.2129389298754079</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U245" t="inlineStr">
         <is>
           <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
-        </is>
-      </c>
-      <c r="W245" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>急性病毒性Ａ型肝炎</t>
-        </is>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD245" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE245" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF245" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG245" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ245" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK245" t="inlineStr">
-        <is>
-          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
-        </is>
-      </c>
-      <c r="AM245" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN245" t="b">
-        <v>1</v>
       </c>
       <c r="AO245" t="inlineStr">
         <is>
@@ -46028,17 +45939,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -46063,7 +45974,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -46072,81 +45983,170 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="O246" t="n">
-        <v>9</v>
-      </c>
-      <c r="R246" t="n">
-        <v>0.007351275668091897</v>
-      </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>49</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>急性病毒性Ａ型肝炎</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN246" t="b">
+        <v>1</v>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
       <c r="AT246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -46178,12 +46178,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -46217,98 +46217,81 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O247" t="n">
-        <v>3</v>
-      </c>
-      <c r="P247" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R247" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="AA247" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ247" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr"/>
       <c r="AT247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46335,7 +46318,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -46387,98 +46370,23 @@
       <c r="P248" t="n">
         <v>3</v>
       </c>
+      <c r="R248" t="n">
+        <v>0.0008595114398308156</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U248" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V248" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W248" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X248" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y248" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD248" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE248" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF248" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG248" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH248" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI248" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ248" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK248" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM248" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN248" t="b">
-        <v>1</v>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
@@ -46572,17 +46480,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -46607,7 +46515,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -46616,20 +46524,42 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P249" t="n">
-        <v>2</v>
-      </c>
-      <c r="R249" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>3</v>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -46637,72 +46567,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM249" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN249" t="b">
+        <v>1</v>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
       <c r="AT249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46729,7 +46717,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -46781,98 +46769,18 @@
       <c r="P250" t="n">
         <v>2</v>
       </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V250" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W250" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X250" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y250" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R250" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD250" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE250" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF250" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG250" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH250" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI250" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ250" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK250" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM250" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN250" t="b">
-        <v>1</v>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
@@ -46966,17 +46874,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -47001,7 +46909,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -47010,81 +46918,173 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O251" t="n">
-        <v>11</v>
-      </c>
-      <c r="R251" t="n">
-        <v>0.00898489248322343</v>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P251" t="n">
+        <v>2</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN251" t="b">
+        <v>1</v>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR251" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
       <c r="AT251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47116,12 +47116,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -47155,98 +47155,81 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O252" t="n">
-        <v>5</v>
-      </c>
-      <c r="P252" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R252" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="AA252" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ252" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47273,7 +47256,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -47325,98 +47308,23 @@
       <c r="P253" t="n">
         <v>5</v>
       </c>
+      <c r="R253" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U253" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE253" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF253" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG253" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN253" t="b">
-        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
@@ -47510,17 +47418,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -47545,7 +47453,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -47554,20 +47462,42 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O254" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P254" t="n">
-        <v>2</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>5</v>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -47575,72 +47505,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN254" t="b">
+        <v>1</v>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ254" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
       <c r="AT254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47667,7 +47655,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -47719,98 +47707,18 @@
       <c r="P255" t="n">
         <v>2</v>
       </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R255" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN255" t="b">
-        <v>1</v>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
@@ -47904,17 +47812,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -47939,7 +47847,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -47948,81 +47856,173 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O256" t="n">
-        <v>13</v>
-      </c>
-      <c r="R256" t="n">
-        <v>0.01061850929835496</v>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P256" t="n">
+        <v>2</v>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM256" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN256" t="b">
+        <v>1</v>
       </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
       <c r="AT256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48054,12 +48054,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -48093,98 +48093,81 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O257" t="n">
-        <v>5</v>
-      </c>
-      <c r="P257" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="R257" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.01061850929835496</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="AA257" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ257" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr"/>
       <c r="AT257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48211,7 +48194,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -48263,98 +48246,23 @@
       <c r="P258" t="n">
         <v>5</v>
       </c>
+      <c r="R258" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U258" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X258" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC258" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD258" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE258" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF258" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG258" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH258" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI258" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM258" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN258" t="b">
-        <v>1</v>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
@@ -48448,17 +48356,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -48483,7 +48391,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -48492,93 +48400,173 @@
         </is>
       </c>
       <c r="N259" t="n">
+        <v>5</v>
+      </c>
+      <c r="O259" t="n">
+        <v>5</v>
+      </c>
+      <c r="P259" t="n">
+        <v>5</v>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM259" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN259" t="b">
         <v>1</v>
       </c>
-      <c r="O259" t="n">
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP259" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT259" t="n">
         <v>1</v>
       </c>
-      <c r="P259" t="n">
-        <v>1</v>
-      </c>
-      <c r="R259" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S259" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA259" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO259" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP259" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ259" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="AT259" t="n">
-        <v>2</v>
-      </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -48605,7 +48593,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -48657,98 +48645,18 @@
       <c r="P260" t="n">
         <v>1</v>
       </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W260" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X260" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y260" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R260" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD260" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE260" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF260" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG260" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ260" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK260" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM260" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN260" t="b">
-        <v>1</v>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
@@ -48842,17 +48750,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -48877,7 +48785,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -48886,81 +48794,173 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O261" t="n">
-        <v>8</v>
-      </c>
-      <c r="R261" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S261" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P261" t="n">
+        <v>1</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM261" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN261" t="b">
+        <v>1</v>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48992,12 +48992,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -49031,98 +49031,81 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O262" t="n">
-        <v>5</v>
-      </c>
-      <c r="P262" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R262" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="AA262" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ262" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr"/>
       <c r="AT262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49149,7 +49132,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -49201,98 +49184,23 @@
       <c r="P263" t="n">
         <v>5</v>
       </c>
+      <c r="R263" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U263" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V263" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W263" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X263" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y263" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD263" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE263" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF263" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG263" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH263" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI263" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ263" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK263" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM263" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN263" t="b">
-        <v>1</v>
       </c>
       <c r="AO263" t="inlineStr">
         <is>
@@ -49386,17 +49294,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -49421,7 +49329,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -49430,81 +49338,173 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O264" t="n">
-        <v>16</v>
-      </c>
-      <c r="R264" t="n">
-        <v>0.01306893452105226</v>
-      </c>
-      <c r="S264" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="P264" t="n">
+        <v>5</v>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ264" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM264" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN264" t="b">
+        <v>1</v>
       </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR264" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -49536,12 +49536,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -49575,93 +49575,81 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="O265" t="n">
-        <v>2</v>
-      </c>
-      <c r="P265" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="R265" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.01306893452105226</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA265" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ265" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49688,7 +49676,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -49740,98 +49728,18 @@
       <c r="P266" t="n">
         <v>2</v>
       </c>
-      <c r="U266" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V266" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W266" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X266" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y266" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R266" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD266" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE266" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF266" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG266" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH266" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI266" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ266" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK266" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM266" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN266" t="b">
-        <v>1</v>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
@@ -49925,17 +49833,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -49960,90 +49868,182 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O267" t="n">
-        <v>0</v>
-      </c>
-      <c r="R267" t="n">
-        <v>0</v>
-      </c>
-      <c r="S267" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P267" t="n">
+        <v>2</v>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI267" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ267" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK267" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM267" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN267" t="b">
+        <v>1</v>
       </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR267" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ267" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
       <c r="AT267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -50075,12 +50075,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -50114,95 +50114,81 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>0.01778809170864137</v>
+        <v>0</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AA268" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ268" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr"/>
       <c r="AT268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -50229,7 +50215,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -50278,98 +50264,23 @@
       <c r="O269" t="n">
         <v>1</v>
       </c>
+      <c r="R269" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U269" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_115</t>
         </is>
       </c>
-      <c r="V269" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="W269" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X269" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y269" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD269" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE269" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF269" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG269" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH269" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI269" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ269" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK269" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
-        </is>
-      </c>
-      <c r="AM269" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN269" t="b">
-        <v>1</v>
       </c>
       <c r="AO269" t="inlineStr">
         <is>
@@ -50463,17 +50374,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -50507,81 +50418,170 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="O270" t="n">
-        <v>99</v>
-      </c>
-      <c r="R270" t="n">
-        <v>0.1918590224554125</v>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
+        </is>
+      </c>
+      <c r="AM270" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN270" t="b">
+        <v>1</v>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
       <c r="AT270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -50613,12 +50613,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -50652,95 +50652,81 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="O271" t="n">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="R271" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.2054248119219569</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ271" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr"/>
       <c r="AT271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -50767,7 +50753,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -50816,98 +50802,23 @@
       <c r="O272" t="n">
         <v>5</v>
       </c>
+      <c r="R272" t="n">
+        <v>0.08844879128977531</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U272" t="inlineStr">
         <is>
           <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>Hepatitt A</t>
-        </is>
-      </c>
-      <c r="Y272" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG272" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ272" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK272" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM272" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN272" t="b">
-        <v>1</v>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
@@ -51001,17 +50912,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -51045,22 +50956,39 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O273" t="n">
-        <v>13</v>
-      </c>
-      <c r="R273" t="n">
-        <v>0.05649400180367965</v>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>Hepatitt A</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -51068,6 +50996,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
+        <v>1</v>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -51085,7 +51071,7 @@
       </c>
       <c r="AS273" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT273" t="n">
@@ -51098,42 +51084,42 @@
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -51160,7 +51146,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -51209,98 +51195,23 @@
       <c r="O274" t="n">
         <v>13</v>
       </c>
+      <c r="R274" t="n">
+        <v>0.05649400180367965</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U274" t="inlineStr">
         <is>
           <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
-      <c r="V274" t="inlineStr">
-        <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
-        </is>
-      </c>
-      <c r="W274" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X274" t="inlineStr">
-        <is>
-          <t>急性病毒性Ａ型肝炎</t>
-        </is>
-      </c>
-      <c r="Y274" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA274" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB274" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD274" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE274" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF274" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG274" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ274" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK274" t="inlineStr">
-        <is>
-          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
-        </is>
-      </c>
-      <c r="AM274" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN274" t="b">
-        <v>1</v>
       </c>
       <c r="AO274" t="inlineStr">
         <is>
@@ -51394,17 +51305,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -51438,35 +51349,107 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O275" t="n">
-        <v>2</v>
-      </c>
-      <c r="P275" t="n">
-        <v>2</v>
-      </c>
-      <c r="R275" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S275" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>急性病毒性Ａ型肝炎</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ275" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK275" t="inlineStr">
+        <is>
+          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
+        </is>
+      </c>
+      <c r="AM275" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN275" t="b">
+        <v>1</v>
       </c>
       <c r="AO275" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP275" t="inlineStr">
@@ -51476,12 +51459,12 @@
       </c>
       <c r="AQ275" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS275" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT275" t="n">
@@ -51489,47 +51472,47 @@
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -51556,7 +51539,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -51608,98 +51591,23 @@
       <c r="P276" t="n">
         <v>2</v>
       </c>
+      <c r="R276" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U276" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V276" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W276" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X276" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y276" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD276" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE276" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF276" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG276" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH276" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI276" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ276" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK276" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM276" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN276" t="b">
-        <v>1</v>
       </c>
       <c r="AO276" t="inlineStr">
         <is>
@@ -51793,17 +51701,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -51828,7 +51736,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -51837,81 +51745,173 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O277" t="n">
-        <v>14</v>
-      </c>
-      <c r="R277" t="n">
-        <v>0.01143531770592073</v>
-      </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P277" t="n">
+        <v>2</v>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN277" t="b">
+        <v>1</v>
       </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR277" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS277" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -51943,12 +51943,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -51982,93 +51982,81 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O278" t="n">
-        <v>1</v>
-      </c>
-      <c r="P278" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R278" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.01143531770592073</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA278" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ278" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr"/>
       <c r="AT278" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -52095,7 +52083,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -52147,98 +52135,18 @@
       <c r="P279" t="n">
         <v>1</v>
       </c>
-      <c r="U279" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V279" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W279" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X279" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y279" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z279" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R279" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB279" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC279" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD279" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE279" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF279" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG279" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH279" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI279" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ279" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK279" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM279" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN279" t="b">
-        <v>1</v>
       </c>
       <c r="AO279" t="inlineStr">
         <is>
@@ -52332,17 +52240,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -52367,7 +52275,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -52376,25 +52284,42 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O280" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P280" t="n">
-        <v>6</v>
-      </c>
-      <c r="R280" t="n">
-        <v>0.001719022879661631</v>
-      </c>
-      <c r="S280" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U280" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -52402,72 +52327,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD280" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI280" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ280" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK280" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM280" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN280" t="b">
+        <v>1</v>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ280" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS280" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -52494,7 +52477,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -52546,98 +52529,23 @@
       <c r="P281" t="n">
         <v>6</v>
       </c>
+      <c r="R281" t="n">
+        <v>0.001719022879661631</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U281" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V281" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W281" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X281" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y281" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z281" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB281" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC281" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD281" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE281" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF281" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG281" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH281" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI281" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ281" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK281" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM281" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN281" t="b">
-        <v>1</v>
       </c>
       <c r="AO281" t="inlineStr">
         <is>
@@ -52731,17 +52639,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -52766,7 +52674,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -52775,81 +52683,173 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O282" t="n">
-        <v>11</v>
-      </c>
-      <c r="R282" t="n">
-        <v>0.00898489248322343</v>
-      </c>
-      <c r="S282" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="P282" t="n">
+        <v>6</v>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD282" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ282" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK282" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM282" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN282" t="b">
+        <v>1</v>
       </c>
       <c r="AO282" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP282" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR282" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS282" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV282" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA282" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB282" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC282" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -52881,12 +52881,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -52920,93 +52920,81 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O283" t="n">
-        <v>2</v>
-      </c>
-      <c r="P283" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R283" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S283" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA283" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO283" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ283" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS283" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr"/>
       <c r="AT283" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV283" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA283" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB283" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC283" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -53033,7 +53021,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -53085,98 +53073,18 @@
       <c r="P284" t="n">
         <v>2</v>
       </c>
-      <c r="U284" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V284" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W284" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X284" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y284" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z284" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R284" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB284" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC284" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD284" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE284" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF284" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG284" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH284" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI284" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ284" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK284" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM284" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN284" t="b">
-        <v>1</v>
       </c>
       <c r="AO284" t="inlineStr">
         <is>
@@ -53270,17 +53178,17 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -53305,7 +53213,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -53314,25 +53222,42 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O285" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P285" t="n">
-        <v>9</v>
-      </c>
-      <c r="R285" t="n">
-        <v>0.002578534319492447</v>
-      </c>
-      <c r="S285" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U285" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -53340,72 +53265,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC285" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD285" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF285" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG285" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH285" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI285" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ285" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK285" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM285" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN285" t="b">
+        <v>1</v>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ285" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS285" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV285" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA285" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB285" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC285" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -53432,7 +53415,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -53484,98 +53467,23 @@
       <c r="P286" t="n">
         <v>9</v>
       </c>
+      <c r="R286" t="n">
+        <v>0.002578534319492447</v>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U286" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V286" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W286" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X286" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y286" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z286" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA286" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB286" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC286" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD286" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE286" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF286" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG286" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH286" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI286" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ286" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK286" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM286" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN286" t="b">
-        <v>1</v>
       </c>
       <c r="AO286" t="inlineStr">
         <is>
@@ -53669,17 +53577,17 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -53704,7 +53612,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -53713,81 +53621,173 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O287" t="n">
-        <v>8</v>
-      </c>
-      <c r="R287" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S287" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="P287" t="n">
+        <v>9</v>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF287" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG287" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH287" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI287" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ287" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK287" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM287" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN287" t="b">
+        <v>1</v>
       </c>
       <c r="AO287" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP287" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR287" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS287" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV287" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA287" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB287" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC287" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -53819,12 +53819,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -53858,93 +53858,81 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O288" t="n">
-        <v>2</v>
-      </c>
-      <c r="P288" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R288" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA288" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO288" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ288" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS288" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR288" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr"/>
       <c r="AT288" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA288" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB288" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC288" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -53971,7 +53959,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -54023,98 +54011,18 @@
       <c r="P289" t="n">
         <v>2</v>
       </c>
-      <c r="U289" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V289" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W289" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X289" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y289" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z289" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R289" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB289" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC289" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD289" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE289" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF289" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG289" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH289" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI289" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ289" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK289" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM289" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN289" t="b">
-        <v>1</v>
       </c>
       <c r="AO289" t="inlineStr">
         <is>
@@ -54208,17 +54116,17 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -54243,7 +54151,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -54252,25 +54160,42 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P290" t="n">
-        <v>3</v>
-      </c>
-      <c r="R290" t="n">
-        <v>0.0008595114398308156</v>
-      </c>
-      <c r="S290" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U290" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -54278,72 +54203,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB290" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC290" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD290" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF290" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG290" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH290" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI290" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ290" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK290" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM290" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN290" t="b">
+        <v>1</v>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP290" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ290" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS290" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV290" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ290" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA290" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB290" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC290" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -54370,7 +54353,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -54422,98 +54405,23 @@
       <c r="P291" t="n">
         <v>3</v>
       </c>
+      <c r="R291" t="n">
+        <v>0.0008595114398308156</v>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U291" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V291" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W291" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X291" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y291" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z291" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA291" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB291" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC291" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD291" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE291" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF291" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG291" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH291" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI291" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ291" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK291" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM291" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN291" t="b">
-        <v>1</v>
       </c>
       <c r="AO291" t="inlineStr">
         <is>
@@ -54579,6 +54487,243 @@
         </is>
       </c>
       <c r="BC291" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>3</v>
+      </c>
+      <c r="O292" t="n">
+        <v>3</v>
+      </c>
+      <c r="P292" t="n">
+        <v>3</v>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z292" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB292" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC292" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD292" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE292" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF292" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG292" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH292" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI292" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ292" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK292" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM292" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN292" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO292" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP292" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ292" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS292" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU292" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV292" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW292" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX292" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY292" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA292" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB292" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC292" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -54700,7 +54845,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -54710,7 +54855,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11">
@@ -54762,7 +54907,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12624</v>
+        <v>12633</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -74743,13 +74743,13 @@
         </is>
       </c>
       <c r="N398" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O398" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R398" t="n">
-        <v>0.05876498911231665</v>
+        <v>0.05141936547327706</v>
       </c>
       <c r="S398" t="inlineStr">
         <is>
@@ -76001,13 +76001,13 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O406" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R406" t="n">
-        <v>0.2461221803215898</v>
+        <v>0.2480601502453819</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
@@ -81641,13 +81641,13 @@
         </is>
       </c>
       <c r="N436" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O436" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R436" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="S436" t="inlineStr">
         <is>
@@ -82300,7 +82300,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17596</v>
+        <v>17597</v>
       </c>
     </row>
     <row r="16">
